--- a/data/trans_bre/P1417-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1417-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,83</t>
+          <t>0,94; 2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,22</t>
+          <t>1,88; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,65</t>
+          <t>0,79; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,85</t>
+          <t>1,01; 4,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,17; 1092,42</t>
+          <t>67,56; 1022,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>152,13; 1453,03</t>
+          <t>156,47; 1532,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 418,14</t>
+          <t>29,5; 425,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 172,61</t>
+          <t>20,77; 177,83</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>354,82%</t>
+          <t>342,01%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,64</t>
+          <t>0,45; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,62</t>
+          <t>0,99; 2,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,4</t>
+          <t>1,05; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,77</t>
+          <t>2,24; 3,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,61; 1242,33</t>
+          <t>77,35; 1446,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>117,83; 1079,46</t>
+          <t>143,07; 1057,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>147,83; 1282,7</t>
+          <t>151,37; 1206,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>165,34; 759,49</t>
+          <t>183,48; 614,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1254,79%</t>
+          <t>1245,52%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,21</t>
+          <t>-0,42; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,67</t>
+          <t>0,87; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,31</t>
+          <t>0,69; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,01</t>
+          <t>2,46; 4,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>284,77; 5093,44</t>
+          <t>338,84; 5245,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>274,86%</t>
+          <t>270,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,83</t>
+          <t>0,8; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,85</t>
+          <t>1,73; 2,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,53</t>
+          <t>1,32; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,84</t>
+          <t>2,58; 3,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>119,47; 735,4</t>
+          <t>125,2; 667,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>242,81; 1009,83</t>
+          <t>261,29; 1011,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>162,67; 590,96</t>
+          <t>154,34; 616,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>160,92; 425,73</t>
+          <t>171,12; 392,07</t>
         </is>
       </c>
     </row>
